--- a/ED_TargetScript_Warthog/MapFiles/HOTAS Switch and Button - Quick Reference - FULL.xlsx
+++ b/ED_TargetScript_Warthog/MapFiles/HOTAS Switch and Button - Quick Reference - FULL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_TargetScript-503\Maps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thrustmaster\ED_TargetScript_Warthog\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FC7390-3705-407D-999A-74173DC06B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49577D60-B2C3-402E-AF6B-AB52F29DB15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="225" windowWidth="33450" windowHeight="18765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="405" windowWidth="23475" windowHeight="16110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="274">
   <si>
     <t>TG1</t>
   </si>
@@ -36,15 +36,6 @@
     <t>TG2</t>
   </si>
   <si>
-    <t>tgHUDMode()</t>
-  </si>
-  <si>
-    <t>tgHardPoints()</t>
-  </si>
-  <si>
-    <t>tgEnhancedFAOFF()</t>
-  </si>
-  <si>
     <t>tgFSSMode()</t>
   </si>
   <si>
@@ -57,9 +48,6 @@
     <t>NextFireGroup</t>
   </si>
   <si>
-    <t>tgLandingGear()</t>
-  </si>
-  <si>
     <t>SelectTargetAhead</t>
   </si>
   <si>
@@ -333,12 +321,6 @@
     <t>OrbitLines</t>
   </si>
   <si>
-    <t>mNAVBeaconWingON/OFF</t>
-  </si>
-  <si>
-    <t>mReportCrimesToggle</t>
-  </si>
-  <si>
     <t>fnRequestDock()</t>
   </si>
   <si>
@@ -384,21 +366,6 @@
     <t>H4L-R</t>
   </si>
   <si>
-    <t>ChargeECM (UP)</t>
-  </si>
-  <si>
-    <t>ChargeECM (DOWN)</t>
-  </si>
-  <si>
-    <t>fnPIPMode(0)</t>
-  </si>
-  <si>
-    <t>fnPIPMode(1)</t>
-  </si>
-  <si>
-    <t>fnPIPMode(2)</t>
-  </si>
-  <si>
     <t>tgReverseThrust(0)</t>
   </si>
   <si>
@@ -417,9 +384,6 @@
     <t>Normal</t>
   </si>
   <si>
-    <t>PWS</t>
-  </si>
-  <si>
     <t>mClearAllChatBox</t>
   </si>
   <si>
@@ -489,15 +453,6 @@
     <t>SCB, SCB+HS</t>
   </si>
   <si>
-    <t>fnHeatsink()</t>
-  </si>
-  <si>
-    <t>Charge ECM</t>
-  </si>
-  <si>
-    <t>Fire ECM</t>
-  </si>
-  <si>
     <t>fnChaff()</t>
   </si>
   <si>
@@ -534,12 +489,6 @@
     <t>Forward</t>
   </si>
   <si>
-    <t>tgText2Speech()</t>
-  </si>
-  <si>
-    <t>EnableVoice ON/OFF</t>
-  </si>
-  <si>
     <t>TargetNextSubsystem</t>
   </si>
   <si>
@@ -747,10 +696,157 @@
     <t>Std FA-Off</t>
   </si>
   <si>
-    <t>tgMouseControl()</t>
-  </si>
-  <si>
-    <t>Mouse Mode for JS</t>
+    <t>tgReportCrimes(0)</t>
+  </si>
+  <si>
+    <t>tgWingBeacon(0)</t>
+  </si>
+  <si>
+    <t>fnSetOriginStation(1)</t>
+  </si>
+  <si>
+    <t>IU</t>
+  </si>
+  <si>
+    <t>OU</t>
+  </si>
+  <si>
+    <t>IM</t>
+  </si>
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>OD</t>
+  </si>
+  <si>
+    <t>tgTxt2Speech()</t>
+  </si>
+  <si>
+    <t>tgOverlay()</t>
+  </si>
+  <si>
+    <t>tgATCChatter()</t>
+  </si>
+  <si>
+    <t>Report Crimes ON/OFF</t>
+  </si>
+  <si>
+    <t>Wing Beacon ON/OFF</t>
+  </si>
+  <si>
+    <t>Set trip timer</t>
+  </si>
+  <si>
+    <t>EDMCOverlay ON/OFF</t>
+  </si>
+  <si>
+    <t>TTS ON/OFF</t>
+  </si>
+  <si>
+    <t>ATCChatter ON/OFF</t>
+  </si>
+  <si>
+    <t>Press+Hold = 'I'</t>
+  </si>
+  <si>
+    <t>tgAxis(SET)</t>
+  </si>
+  <si>
+    <t>tgHUDMode(0)</t>
+  </si>
+  <si>
+    <t>tgHardPoints(0)</t>
+  </si>
+  <si>
+    <t>Combat/Analysis</t>
+  </si>
+  <si>
+    <t>Deployed/Stowed</t>
+  </si>
+  <si>
+    <t>Pulse Wave Scan</t>
+  </si>
+  <si>
+    <t>tgEnhancedFAOFF(0)</t>
+  </si>
+  <si>
+    <t>tgLandingGear(0)</t>
+  </si>
+  <si>
+    <t>tgLandingGear(2)</t>
+  </si>
+  <si>
+    <t>Toggle Autoretract</t>
+  </si>
+  <si>
+    <t>Toggle Autodeploy</t>
+  </si>
+  <si>
+    <t>tgLandingGear(30</t>
+  </si>
+  <si>
+    <t>tgLights(2)</t>
+  </si>
+  <si>
+    <t>Auto when docking</t>
+  </si>
+  <si>
+    <t>Front/Back</t>
+  </si>
+  <si>
+    <t>FighterAttack</t>
+  </si>
+  <si>
+    <t>FighterNoFire</t>
+  </si>
+  <si>
+    <t>FighterHold</t>
+  </si>
+  <si>
+    <t>FighterDefend</t>
+  </si>
+  <si>
+    <t>FighterFollow</t>
+  </si>
+  <si>
+    <t>FighterAgresive</t>
+  </si>
+  <si>
+    <t>fnHeatsink(1)</t>
+  </si>
+  <si>
+    <t>fnHeatsink(0)</t>
+  </si>
+  <si>
+    <t>toggle autosink @ 100%</t>
+  </si>
+  <si>
+    <t>ChargeECM</t>
+  </si>
+  <si>
+    <t>Hold to Charge ECM</t>
+  </si>
+  <si>
+    <t>Release to fire ECM</t>
+  </si>
+  <si>
+    <t>fnPIPMode(RESET)</t>
+  </si>
+  <si>
+    <t>fnPIPMode(Previous)</t>
+  </si>
+  <si>
+    <t>fnPIPMode(Next)</t>
+  </si>
+  <si>
+    <t>tgAutoPIPS()</t>
+  </si>
+  <si>
+    <t>when docking</t>
   </si>
 </sst>
 </file>
@@ -774,7 +870,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -799,12 +895,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="33">
     <border>
@@ -1379,20 +1469,56 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1409,46 +1535,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1741,12 +1831,12 @@
     <col min="2" max="2" width="13.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="5.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="5.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="27.140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="1.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5.7109375" style="1" customWidth="1"/>
@@ -1761,7 +1851,7 @@
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="54" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="C2" s="55"/>
       <c r="D2" s="55"/>
@@ -1779,1978 +1869,2062 @@
     </row>
     <row r="3" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="G4" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
-      <c r="L4" s="61" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="63"/>
+      <c r="B4" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
+      <c r="G4" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="60"/>
+      <c r="L4" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="60"/>
     </row>
     <row r="5" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="E7" s="12"/>
       <c r="G7" s="26" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H7" s="33"/>
       <c r="I7" s="27" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J7" s="18"/>
-      <c r="L7" s="47" t="s">
-        <v>73</v>
+      <c r="L7" s="48" t="s">
+        <v>69</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="O7" s="12"/>
     </row>
     <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="45"/>
+      <c r="B8" s="50"/>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H8" s="34"/>
       <c r="I8" s="17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="J8" s="19"/>
-      <c r="L8" s="46"/>
+      <c r="L8" s="49"/>
       <c r="M8" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="N8" s="22" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="46"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H9" s="23"/>
       <c r="I9" s="32" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J9" s="20"/>
       <c r="L9" s="25" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M9" s="35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="O9" s="36"/>
     </row>
     <row r="10" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="57" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
-      <c r="L10" s="47" t="s">
-        <v>75</v>
+      <c r="L10" s="48" t="s">
+        <v>71</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="O10" s="12"/>
     </row>
     <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="60"/>
+      <c r="B11" s="57"/>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="21"/>
-      <c r="G11" s="57" t="s">
-        <v>50</v>
+      <c r="G11" s="51" t="s">
+        <v>46</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J11" s="12"/>
-      <c r="L11" s="46"/>
+      <c r="L11" s="49"/>
       <c r="M11" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="N11" s="22" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="46"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="5"/>
-      <c r="G12" s="58"/>
+      <c r="G12" s="52"/>
       <c r="H12" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G13" s="59"/>
+      <c r="G13" s="53"/>
       <c r="H13" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="5"/>
-      <c r="L13" s="47" t="s">
-        <v>76</v>
+      <c r="L13" s="48" t="s">
+        <v>72</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="O13" s="12"/>
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="47" t="s">
-        <v>27</v>
+      <c r="B14" s="48" t="s">
+        <v>23</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="12"/>
+        <v>243</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>245</v>
+      </c>
       <c r="G14" s="13"/>
-      <c r="L14" s="46"/>
+      <c r="L14" s="49"/>
       <c r="M14" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="45"/>
+      <c r="B15" s="50"/>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="G15" s="57" t="s">
-        <v>53</v>
+        <v>244</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>49</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="J15" s="12"/>
-      <c r="L15" s="45" t="s">
-        <v>77</v>
+      <c r="L15" s="50" t="s">
+        <v>73</v>
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="46"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="G16" s="58"/>
+        <v>242</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" s="52"/>
       <c r="H16" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="L16" s="45"/>
+      <c r="L16" s="50"/>
       <c r="M16" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="16"/>
-      <c r="G17" s="59"/>
+      <c r="G17" s="53"/>
       <c r="H17" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="5"/>
-      <c r="L17" s="46"/>
+      <c r="L17" s="49"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="5"/>
     </row>
     <row r="18" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="47" t="s">
-        <v>108</v>
+      <c r="B18" s="48" t="s">
+        <v>102</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="G18" s="13"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="45"/>
+      <c r="B19" s="50"/>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" s="47" t="s">
-        <v>55</v>
+        <v>118</v>
+      </c>
+      <c r="G19" s="48" t="s">
+        <v>51</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="J19" s="12"/>
-      <c r="L19" s="47" t="s">
-        <v>78</v>
+      <c r="L19" s="48" t="s">
+        <v>74</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="O19" s="12"/>
     </row>
     <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="46"/>
+      <c r="B20" s="49"/>
       <c r="C20" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G20" s="48"/>
+        <v>186</v>
+      </c>
+      <c r="G20" s="47"/>
       <c r="H20" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="L20" s="45"/>
+        <v>147</v>
+      </c>
+      <c r="L20" s="50"/>
       <c r="M20" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="3"/>
     </row>
     <row r="21" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="16"/>
-      <c r="G21" s="44" t="s">
-        <v>56</v>
+      <c r="G21" s="46" t="s">
+        <v>52</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="L21" s="45"/>
+      <c r="L21" s="50"/>
       <c r="M21" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="3"/>
     </row>
     <row r="22" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="30" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C22" s="31"/>
       <c r="D22" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="29"/>
-      <c r="G22" s="48"/>
+        <v>108</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="G22" s="47"/>
       <c r="H22" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L22" s="45"/>
+        <v>150</v>
+      </c>
+      <c r="L22" s="50"/>
       <c r="M22" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="O22" s="3"/>
     </row>
     <row r="23" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G23" s="44" t="s">
-        <v>57</v>
+      <c r="G23" s="46" t="s">
+        <v>53</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="J23" s="3"/>
-      <c r="L23" s="46"/>
+      <c r="L23" s="49"/>
       <c r="M23" s="22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N23" s="22"/>
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="47" t="s">
-        <v>28</v>
+      <c r="B24" s="48" t="s">
+        <v>24</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="66" t="s">
-        <v>240</v>
-      </c>
-      <c r="E24" s="67" t="s">
-        <v>241</v>
-      </c>
-      <c r="G24" s="48"/>
+        <v>20</v>
+      </c>
+      <c r="D24" s="66"/>
+      <c r="E24" s="67"/>
+      <c r="G24" s="47"/>
       <c r="H24" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J24" s="3"/>
-      <c r="L24" s="47" t="s">
-        <v>79</v>
+      <c r="L24" s="48" t="s">
+        <v>75</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N24" s="11"/>
       <c r="O24" s="12"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="45"/>
+      <c r="B25" s="50"/>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>248</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G25" s="44" t="s">
-        <v>58</v>
+        <v>222</v>
+      </c>
+      <c r="G25" s="46" t="s">
+        <v>54</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="J25" s="3"/>
-      <c r="L25" s="45"/>
+      <c r="L25" s="50"/>
       <c r="M25" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="O25" s="3"/>
     </row>
     <row r="26" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="46"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="5"/>
-      <c r="G26" s="46"/>
+      <c r="G26" s="49"/>
       <c r="H26" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J26" s="5"/>
-      <c r="L26" s="46"/>
+      <c r="L26" s="49"/>
       <c r="M26" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="5"/>
     </row>
     <row r="27" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="47" t="s">
-        <v>29</v>
+      <c r="B28" s="48" t="s">
+        <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E28" s="12"/>
       <c r="G28" s="26" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="L28" s="47" t="s">
-        <v>80</v>
+        <v>206</v>
+      </c>
+      <c r="L28" s="48" t="s">
+        <v>76</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O28" s="12"/>
     </row>
     <row r="29" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="45"/>
+      <c r="B29" s="50"/>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E29" s="3"/>
       <c r="G29" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="L29" s="46"/>
+        <v>206</v>
+      </c>
+      <c r="L29" s="49"/>
       <c r="M29" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="48"/>
+      <c r="B30" s="47"/>
       <c r="C30" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E30" s="3"/>
       <c r="G30" s="15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="44" t="s">
-        <v>30</v>
+      <c r="B31" s="46" t="s">
+        <v>26</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="3"/>
       <c r="G31" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="L31" s="47" t="s">
-        <v>81</v>
+        <v>206</v>
+      </c>
+      <c r="L31" s="48" t="s">
+        <v>77</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="O31" s="12"/>
     </row>
     <row r="32" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="45"/>
+      <c r="B32" s="50"/>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="G32" s="44" t="s">
-        <v>63</v>
+      <c r="G32" s="46" t="s">
+        <v>59</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J32" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="L32" s="46"/>
+        <v>209</v>
+      </c>
+      <c r="J32" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="L32" s="49"/>
       <c r="M32" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="O32" s="5"/>
     </row>
     <row r="33" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="48"/>
+      <c r="B33" s="47"/>
       <c r="C33" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="3"/>
-      <c r="G33" s="48"/>
+      <c r="G33" s="47"/>
       <c r="H33" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J33" s="65"/>
+        <v>210</v>
+      </c>
+      <c r="J33" s="45"/>
     </row>
     <row r="34" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="44" t="s">
-        <v>31</v>
+      <c r="B34" s="46" t="s">
+        <v>27</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>251</v>
+      </c>
       <c r="G34" s="37" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="H34" s="22"/>
       <c r="I34" s="22" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="L34" s="47" t="s">
-        <v>82</v>
+        <v>206</v>
+      </c>
+      <c r="L34" s="48" t="s">
+        <v>78</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="O34" s="12"/>
     </row>
     <row r="35" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45"/>
+      <c r="B35" s="50"/>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>10</v>
+        <v>249</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L35" s="45"/>
+        <v>129</v>
+      </c>
+      <c r="L35" s="50"/>
       <c r="M35" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="48"/>
+      <c r="B36" s="47"/>
       <c r="C36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="3"/>
-      <c r="G36" s="47" t="s">
-        <v>64</v>
+        <v>22</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G36" s="48" t="s">
+        <v>60</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="L36" s="48"/>
+        <v>151</v>
+      </c>
+      <c r="L36" s="47"/>
       <c r="M36" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="O36" s="3"/>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="44" t="s">
-        <v>32</v>
+      <c r="B37" s="46" t="s">
+        <v>28</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G37" s="45"/>
+        <v>131</v>
+      </c>
+      <c r="G37" s="50"/>
       <c r="H37" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="L37" s="44" t="s">
-        <v>181</v>
+        <v>152</v>
+      </c>
+      <c r="L37" s="46" t="s">
+        <v>164</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="3"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="45"/>
+      <c r="B38" s="50"/>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G38" s="48"/>
+        <v>129</v>
+      </c>
+      <c r="G38" s="47"/>
       <c r="H38" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="L38" s="45"/>
+        <v>211</v>
+      </c>
+      <c r="L38" s="50"/>
       <c r="M38" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="46"/>
+      <c r="B39" s="49"/>
       <c r="C39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>255</v>
+      </c>
       <c r="G39" s="15" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L39" s="48"/>
+        <v>153</v>
+      </c>
+      <c r="L39" s="47"/>
       <c r="M39" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="3"/>
     </row>
     <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G40" s="45" t="s">
-        <v>66</v>
+      <c r="G40" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="7"/>
-      <c r="L40" s="44" t="s">
-        <v>83</v>
+      <c r="L40" s="46" t="s">
+        <v>79</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="3"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B41" s="47" t="s">
-        <v>33</v>
+      <c r="B41" s="48" t="s">
+        <v>29</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" s="12"/>
-      <c r="G41" s="45"/>
+        <v>133</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="G41" s="50"/>
       <c r="H41" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J41" s="3"/>
-      <c r="L41" s="45"/>
+      <c r="L41" s="50"/>
       <c r="M41" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="3"/>
     </row>
     <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="45"/>
+      <c r="B42" s="50"/>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E42" s="3"/>
-      <c r="G42" s="46"/>
+      <c r="G42" s="49"/>
       <c r="H42" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="5"/>
-      <c r="L42" s="48"/>
+      <c r="L42" s="47"/>
       <c r="M42" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N42" s="24"/>
       <c r="O42" s="3"/>
     </row>
     <row r="43" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="48"/>
+      <c r="B43" s="47"/>
       <c r="C43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D43" s="2"/>
       <c r="E43" s="3"/>
-      <c r="L43" s="44" t="s">
-        <v>84</v>
+      <c r="L43" s="46" t="s">
+        <v>80</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N43" s="24" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="O43" s="3"/>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="44" t="s">
-        <v>34</v>
+      <c r="B44" s="46" t="s">
+        <v>30</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3"/>
-      <c r="G44" s="47" t="s">
-        <v>68</v>
+      <c r="G44" s="48" t="s">
+        <v>64</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>24</v>
+        <v>226</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="J44" s="12"/>
-      <c r="L44" s="45"/>
+        <v>223</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="L44" s="50"/>
       <c r="M44" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N44" s="24" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="45"/>
+      <c r="B45" s="50"/>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J45" s="3"/>
-      <c r="L45" s="48"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="L45" s="47"/>
       <c r="M45" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N45" s="24" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="O45" s="3"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="48"/>
+      <c r="B46" s="47"/>
       <c r="C46" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E46" s="3"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="L46" s="45" t="s">
-        <v>183</v>
+      <c r="G46" s="50"/>
+      <c r="H46" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="7"/>
+      <c r="L46" s="50" t="s">
+        <v>166</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="3"/>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="44" t="s">
-        <v>35</v>
+      <c r="B47" s="46" t="s">
+        <v>31</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="3"/>
-      <c r="G47" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="3"/>
-      <c r="L47" s="45"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="L47" s="50"/>
       <c r="M47" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="45"/>
+      <c r="B48" s="50"/>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E48" s="3"/>
-      <c r="G48" s="45"/>
+      <c r="G48" s="50"/>
       <c r="H48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="3"/>
-      <c r="L48" s="46"/>
+        <v>230</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="L48" s="49"/>
       <c r="M48" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="O48" s="5"/>
     </row>
     <row r="49" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="48"/>
+      <c r="B49" s="47"/>
       <c r="C49" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E49" s="3"/>
-      <c r="G49" s="48"/>
+      <c r="G49" s="47"/>
       <c r="H49" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="3"/>
+        <v>231</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="44" t="s">
-        <v>36</v>
+      <c r="B50" s="46" t="s">
+        <v>32</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="3"/>
-      <c r="G50" s="44" t="s">
-        <v>70</v>
+      <c r="G50" s="46" t="s">
+        <v>65</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>103</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I50" s="2"/>
       <c r="J50" s="3"/>
-      <c r="L50" s="47" t="s">
-        <v>85</v>
+      <c r="L50" s="48" t="s">
+        <v>81</v>
       </c>
       <c r="M50" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N50" s="11"/>
       <c r="O50" s="12"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B51" s="45"/>
+      <c r="B51" s="50"/>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E51" s="3"/>
-      <c r="G51" s="45"/>
+      <c r="G51" s="50"/>
       <c r="H51" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I51" s="2"/>
       <c r="J51" s="3"/>
-      <c r="L51" s="45"/>
+      <c r="L51" s="50"/>
       <c r="M51" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="O51" s="3"/>
     </row>
     <row r="52" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="46"/>
+      <c r="B52" s="49"/>
       <c r="C52" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E52" s="5"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I52" s="4"/>
-      <c r="J52" s="5"/>
-      <c r="L52" s="48"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="3"/>
+      <c r="L52" s="47"/>
       <c r="M52" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="3"/>
     </row>
     <row r="53" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L53" s="44" t="s">
-        <v>86</v>
+      <c r="G53" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="3"/>
+      <c r="L53" s="46" t="s">
+        <v>82</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="3"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B54" s="47" t="s">
-        <v>37</v>
+      <c r="B54" s="48" t="s">
+        <v>33</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>257</v>
+      </c>
       <c r="E54" s="12"/>
-      <c r="G54" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I54" s="11"/>
-      <c r="J54" s="12"/>
-      <c r="L54" s="45"/>
+      <c r="G54" s="50"/>
+      <c r="H54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" s="3"/>
+      <c r="L54" s="50"/>
       <c r="M54" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="O54" s="3"/>
     </row>
     <row r="55" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="45"/>
+      <c r="B55" s="50"/>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E55" s="3"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="J55" s="3"/>
-      <c r="L55" s="46"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="L55" s="49"/>
       <c r="M55" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="5"/>
     </row>
     <row r="56" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="48"/>
+      <c r="B56" s="47"/>
       <c r="C56" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="3"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I56" s="2"/>
-      <c r="J56" s="3"/>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B57" s="44" t="s">
-        <v>38</v>
+      <c r="B57" s="46" t="s">
+        <v>34</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>258</v>
+      </c>
       <c r="E57" s="3"/>
-      <c r="G57" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="3"/>
-      <c r="L57" s="47" t="s">
-        <v>87</v>
+      <c r="G57" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="11"/>
+      <c r="J57" s="12"/>
+      <c r="L57" s="48" t="s">
+        <v>83</v>
       </c>
       <c r="M57" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N57" s="11"/>
       <c r="O57" s="12"/>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B58" s="45"/>
+      <c r="B58" s="50"/>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E58" s="3"/>
-      <c r="G58" s="45"/>
+      <c r="G58" s="50"/>
       <c r="H58" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I58" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J58" s="3"/>
+      <c r="L58" s="50"/>
+      <c r="M58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="O58" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="J58" s="3"/>
-      <c r="L58" s="45"/>
-      <c r="M58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="48"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B59" s="47"/>
       <c r="C59" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D59" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>259</v>
+      </c>
       <c r="E59" s="3"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I59" s="4"/>
-      <c r="J59" s="5"/>
-      <c r="L59" s="48"/>
+      <c r="G59" s="47"/>
+      <c r="H59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="3"/>
+      <c r="L59" s="47"/>
       <c r="M59" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="3"/>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B60" s="44" t="s">
-        <v>39</v>
+      <c r="B60" s="46" t="s">
+        <v>35</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D60" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>260</v>
+      </c>
       <c r="E60" s="3"/>
-      <c r="L60" s="44" t="s">
-        <v>88</v>
+      <c r="G60" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="3"/>
+      <c r="L60" s="46" t="s">
+        <v>84</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="3"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B61" s="45"/>
+      <c r="B61" s="50"/>
       <c r="C61" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E61" s="3"/>
-      <c r="L61" s="45"/>
+      <c r="G61" s="50"/>
+      <c r="H61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J61" s="3"/>
+      <c r="L61" s="50"/>
       <c r="M61" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="3"/>
     </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B62" s="48"/>
+    <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="47"/>
       <c r="C62" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D62" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="E62" s="3"/>
-      <c r="L62" s="48"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" s="4"/>
+      <c r="J62" s="5"/>
+      <c r="L62" s="47"/>
       <c r="M62" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="3"/>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B63" s="44" t="s">
-        <v>40</v>
+      <c r="B63" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D63" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="E63" s="3"/>
-      <c r="L63" s="44" t="s">
-        <v>89</v>
+      <c r="L63" s="46" t="s">
+        <v>85</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="3"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B64" s="45"/>
+      <c r="B64" s="50"/>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="L64" s="45"/>
+      <c r="L64" s="50"/>
       <c r="M64" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="46"/>
+      <c r="B65" s="49"/>
       <c r="C65" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="5"/>
-      <c r="L65" s="48"/>
+      <c r="L65" s="47"/>
       <c r="M65" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="3"/>
     </row>
     <row r="66" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L66" s="14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M66" s="4"/>
       <c r="N66" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O66" s="5" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="47" t="s">
-        <v>41</v>
+      <c r="B67" s="48" t="s">
+        <v>37</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B68" s="45"/>
+      <c r="B68" s="50"/>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="L68" s="47" t="s">
-        <v>91</v>
+        <v>141</v>
+      </c>
+      <c r="L68" s="48" t="s">
+        <v>87</v>
       </c>
       <c r="M68" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N68" s="11" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="O68" s="12" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B69" s="48"/>
+      <c r="B69" s="47"/>
       <c r="C69" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E69" s="3"/>
-      <c r="L69" s="45"/>
+      <c r="L69" s="50"/>
       <c r="M69" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B70" s="44" t="s">
-        <v>42</v>
+      <c r="B70" s="46" t="s">
+        <v>38</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="3"/>
-      <c r="L70" s="48"/>
+        <v>20</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L70" s="47"/>
       <c r="M70" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B71" s="45"/>
+      <c r="B71" s="50"/>
       <c r="C71" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>154</v>
+        <v>264</v>
       </c>
       <c r="E71" s="3"/>
-      <c r="L71" s="44" t="s">
-        <v>92</v>
+      <c r="L71" s="46" t="s">
+        <v>88</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="3"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B72" s="48"/>
+      <c r="B72" s="47"/>
       <c r="C72" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E72" s="3"/>
-      <c r="L72" s="45"/>
+      <c r="L72" s="50"/>
       <c r="M72" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="3"/>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B73" s="44" t="s">
-        <v>43</v>
+      <c r="B73" s="46" t="s">
+        <v>39</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3"/>
-      <c r="L73" s="48"/>
+      <c r="L73" s="47"/>
       <c r="M73" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="3"/>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B74" s="45"/>
+      <c r="B74" s="50"/>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>120</v>
+        <v>266</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="L74" s="44" t="s">
-        <v>93</v>
+        <v>267</v>
+      </c>
+      <c r="L74" s="46" t="s">
+        <v>89</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="3"/>
     </row>
     <row r="75" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B75" s="48"/>
+      <c r="B75" s="47"/>
       <c r="C75" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E75" s="3"/>
-      <c r="L75" s="45"/>
+      <c r="L75" s="50"/>
       <c r="M75" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="44" t="s">
-        <v>118</v>
+      <c r="B76" s="46" t="s">
+        <v>112</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D76" s="2">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D76" s="2"/>
       <c r="E76" s="3"/>
-      <c r="L76" s="46"/>
+      <c r="L76" s="49"/>
       <c r="M76" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N76" s="4"/>
       <c r="O76" s="5"/>
     </row>
     <row r="77" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="45"/>
+      <c r="B77" s="50"/>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>119</v>
+        <v>266</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>156</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B78" s="48"/>
+      <c r="B78" s="47"/>
       <c r="C78" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D78" s="2">
-        <v>0</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D78" s="2"/>
       <c r="E78" s="3"/>
-      <c r="L78" s="47" t="s">
-        <v>94</v>
+      <c r="L78" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="M78" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N78" s="11" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="O78" s="12"/>
     </row>
     <row r="79" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B79" s="44" t="s">
-        <v>44</v>
+      <c r="B79" s="46" t="s">
+        <v>40</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="3"/>
-      <c r="L79" s="45"/>
+      <c r="L79" s="50"/>
       <c r="M79" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B80" s="45"/>
+      <c r="B80" s="50"/>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="E80" s="3"/>
-      <c r="L80" s="48"/>
+      <c r="L80" s="47"/>
       <c r="M80" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="O80" s="3"/>
     </row>
     <row r="81" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B81" s="48"/>
+      <c r="B81" s="47"/>
       <c r="C81" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E81" s="3"/>
-      <c r="L81" s="44" t="s">
-        <v>95</v>
+      <c r="L81" s="46" t="s">
+        <v>91</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="3"/>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B82" s="44" t="s">
-        <v>22</v>
+      <c r="B82" s="46" t="s">
+        <v>18</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="L82" s="45"/>
+        <v>226</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" s="3"/>
+      <c r="L82" s="50"/>
       <c r="M82" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="3"/>
     </row>
     <row r="83" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="45"/>
+      <c r="B83" s="50"/>
       <c r="C83" s="2" t="s">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>122</v>
+        <v>269</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="L83" s="46"/>
+        <v>143</v>
+      </c>
+      <c r="L83" s="49"/>
       <c r="M83" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="5"/>
     </row>
     <row r="84" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="46"/>
-      <c r="C84" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>160</v>
+      <c r="B84" s="50"/>
+      <c r="C84" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L85" s="47" t="s">
-        <v>96</v>
+      <c r="B85" s="50"/>
+      <c r="C85" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L85" s="48" t="s">
+        <v>92</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N85" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="O85" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B86" s="50"/>
+      <c r="C86" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="3"/>
+      <c r="L86" s="50"/>
+      <c r="M86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="87" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="49"/>
+      <c r="C87" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="L87" s="47"/>
+      <c r="M87" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="O87" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="O85" s="12" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L86" s="45"/>
-      <c r="M86" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N86" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O86" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L87" s="48"/>
-      <c r="M87" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="88" spans="2:15" x14ac:dyDescent="0.25">
       <c r="L88" s="25" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L89" s="44" t="s">
-        <v>107</v>
+      <c r="L89" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="3"/>
     </row>
     <row r="90" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L90" s="45"/>
+      <c r="L90" s="50"/>
       <c r="M90" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="3"/>
     </row>
     <row r="91" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L91" s="46"/>
+      <c r="L91" s="49"/>
       <c r="M91" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N91" s="4"/>
       <c r="O91" s="5"/>
     </row>
     <row r="92" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="93" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L93" s="47" t="s">
-        <v>99</v>
+      <c r="L93" s="48" t="s">
+        <v>95</v>
       </c>
       <c r="M93" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N93" s="11"/>
       <c r="O93" s="12"/>
     </row>
     <row r="94" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L94" s="45"/>
+      <c r="L94" s="50"/>
       <c r="M94" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="95" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L95" s="48"/>
+      <c r="L95" s="47"/>
       <c r="M95" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="3"/>
     </row>
     <row r="96" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="L96" s="44" t="s">
-        <v>199</v>
+      <c r="L96" s="46" t="s">
+        <v>182</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="3"/>
     </row>
     <row r="97" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L97" s="45"/>
+      <c r="L97" s="50"/>
       <c r="M97" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L98" s="46"/>
+      <c r="L98" s="49"/>
       <c r="M98" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N98" s="4"/>
       <c r="O98" s="5"/>
     </row>
     <row r="99" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="100" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L100" s="49" t="s">
-        <v>97</v>
+      <c r="L100" s="61" t="s">
+        <v>93</v>
       </c>
       <c r="M100" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N100" s="38"/>
       <c r="O100" s="39"/>
     </row>
     <row r="101" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L101" s="50"/>
+      <c r="L101" s="62"/>
       <c r="M101" s="40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N101" s="40"/>
       <c r="O101" s="41"/>
     </row>
     <row r="102" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L102" s="51"/>
+      <c r="L102" s="63"/>
       <c r="M102" s="40" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N102" s="40"/>
       <c r="O102" s="41"/>
     </row>
     <row r="103" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L103" s="52" t="s">
-        <v>98</v>
+      <c r="L103" s="64" t="s">
+        <v>94</v>
       </c>
       <c r="M103" s="40" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N103" s="40"/>
       <c r="O103" s="41"/>
     </row>
     <row r="104" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L104" s="50"/>
+      <c r="L104" s="62"/>
       <c r="M104" s="40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N104" s="40"/>
       <c r="O104" s="41"/>
     </row>
     <row r="105" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L105" s="53"/>
+      <c r="L105" s="65"/>
       <c r="M105" s="42" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N105" s="42"/>
       <c r="O105" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="J32:J33"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="L24:L26"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="L19:L23"/>
-    <mergeCell ref="L50:L52"/>
-    <mergeCell ref="L34:L36"/>
-    <mergeCell ref="L40:L42"/>
-    <mergeCell ref="L46:L48"/>
-    <mergeCell ref="L37:L39"/>
-    <mergeCell ref="L43:L45"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="G50:G52"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="G36:G38"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="B82:B87"/>
+    <mergeCell ref="L53:L55"/>
+    <mergeCell ref="L57:L59"/>
+    <mergeCell ref="L60:L62"/>
+    <mergeCell ref="L63:L65"/>
+    <mergeCell ref="L71:L73"/>
+    <mergeCell ref="L74:L76"/>
+    <mergeCell ref="L78:L80"/>
+    <mergeCell ref="L81:L83"/>
+    <mergeCell ref="L68:L70"/>
+    <mergeCell ref="L93:L95"/>
+    <mergeCell ref="L96:L98"/>
+    <mergeCell ref="L100:L102"/>
+    <mergeCell ref="L85:L87"/>
+    <mergeCell ref="L103:L105"/>
+    <mergeCell ref="L89:L91"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="L15:L17"/>
     <mergeCell ref="B67:B69"/>
     <mergeCell ref="B70:B72"/>
     <mergeCell ref="B73:B75"/>
@@ -3765,34 +3939,35 @@
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="G40:G42"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="L96:L98"/>
-    <mergeCell ref="L100:L102"/>
-    <mergeCell ref="L85:L87"/>
-    <mergeCell ref="L103:L105"/>
-    <mergeCell ref="L89:L91"/>
-    <mergeCell ref="L74:L76"/>
-    <mergeCell ref="L78:L80"/>
-    <mergeCell ref="L81:L83"/>
-    <mergeCell ref="L68:L70"/>
-    <mergeCell ref="L93:L95"/>
-    <mergeCell ref="L53:L55"/>
-    <mergeCell ref="L57:L59"/>
-    <mergeCell ref="L60:L62"/>
-    <mergeCell ref="L63:L65"/>
-    <mergeCell ref="L71:L73"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="G44:G49"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="G50:G52"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="L24:L26"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="L19:L23"/>
+    <mergeCell ref="L50:L52"/>
+    <mergeCell ref="L34:L36"/>
+    <mergeCell ref="L40:L42"/>
+    <mergeCell ref="L46:L48"/>
+    <mergeCell ref="L37:L39"/>
+    <mergeCell ref="L43:L45"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="G25:G26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="44" orientation="portrait" r:id="rId1"/>
